--- a/data/trans_orig/P57_AC_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P57_AC_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo confidencial bajo (Duke) en 2007</t>
+          <t>Población con apoyo confidencial bajo (Duke) en 2007 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>736039</t>
+          <t>736167</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>791738</t>
+          <t>792507</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>994244</t>
+          <t>993030</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1055751</t>
+          <t>1051308</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1750075</t>
+          <t>1750425</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1828625</t>
+          <t>1829589</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,96%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>239985</t>
+          <t>239216</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>295684</t>
+          <t>295556</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>259362</t>
+          <t>263805</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>320869</t>
+          <t>322083</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>518210</t>
+          <t>517246</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>596760</t>
+          <t>596410</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,41%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1055541</t>
+          <t>1050497</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1132512</t>
+          <t>1130738</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1028904</t>
+          <t>1028919</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1102731</t>
+          <t>1101192</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2102038</t>
+          <t>2105424</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2211951</t>
+          <t>2213999</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>67,52%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>560901</t>
+          <t>562675</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>637872</t>
+          <t>642916</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>482811</t>
+          <t>484350</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>556638</t>
+          <t>556623</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1067004</t>
+          <t>1064956</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1176917</t>
+          <t>1173531</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,79%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>344120</t>
+          <t>343119</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>388052</t>
+          <t>389365</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>276310</t>
+          <t>274122</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>319443</t>
+          <t>316966</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>634024</t>
+          <t>632411</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>695848</t>
+          <t>695823</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>67,87%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>160721</t>
+          <t>159408</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>204653</t>
+          <t>205654</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>156969</t>
+          <t>159446</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>200102</t>
+          <t>202290</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>329337</t>
+          <t>329362</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>391161</t>
+          <t>392774</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,31%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2170969</t>
+          <t>2172811</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2275537</t>
+          <t>2281084</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2333250</t>
+          <t>2334164</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2435811</t>
+          <t>2444053</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4539778</t>
+          <t>4540249</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4688116</t>
+          <t>4681898</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,39%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>998372</t>
+          <t>992825</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1102940</t>
+          <t>1101098</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>941255</t>
+          <t>933013</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1043816</t>
+          <t>1042902</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1962859</t>
+          <t>1969077</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2111197</t>
+          <t>2110726</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo confidencial bajo (Duke) en 2012</t>
+          <t>Población con apoyo confidencial bajo (Duke) en 2012 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>649594</t>
+          <t>646955</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>709356</t>
+          <t>705347</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>974164</t>
+          <t>974431</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1037709</t>
+          <t>1039179</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1644221</t>
+          <t>1644301</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1728739</t>
+          <t>1734744</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,74%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>252401</t>
+          <t>256410</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>312163</t>
+          <t>314802</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>290860</t>
+          <t>289390</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>354405</t>
+          <t>354138</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>561587</t>
+          <t>555582</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>646105</t>
+          <t>646025</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1226874</t>
+          <t>1225536</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1314122</t>
+          <t>1312062</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1248401</t>
+          <t>1245026</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1325393</t>
+          <t>1325305</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2497826</t>
+          <t>2489227</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2612534</t>
+          <t>2608103</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,42%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>638713</t>
+          <t>640773</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>725961</t>
+          <t>727299</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>425669</t>
+          <t>425757</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>502661</t>
+          <t>506036</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1091363</t>
+          <t>1095794</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1206071</t>
+          <t>1214670</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,79%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>278752</t>
+          <t>278510</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>324413</t>
+          <t>323951</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>268658</t>
+          <t>268891</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>313829</t>
+          <t>311597</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>565020</t>
+          <t>562693</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>629966</t>
+          <t>627297</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,31%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>152996</t>
+          <t>153458</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>198657</t>
+          <t>198899</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>140693</t>
+          <t>142925</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>185864</t>
+          <t>185631</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>301965</t>
+          <t>304634</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>366911</t>
+          <t>369238</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,62%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2189613</t>
+          <t>2194927</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2301491</t>
+          <t>2303614</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2525973</t>
+          <t>2531121</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2638798</t>
+          <t>2635431</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4757309</t>
+          <t>4756135</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4912934</t>
+          <t>4916123</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,98%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1090509</t>
+          <t>1088386</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1202387</t>
+          <t>1197073</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>895355</t>
+          <t>898722</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1008180</t>
+          <t>1003032</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2013220</t>
+          <t>2010031</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2168845</t>
+          <t>2170019</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,33%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo confidencial bajo (Duke) en 2016</t>
+          <t>Población con apoyo confidencial bajo (Duke) en 2016 (tasa de respuesta: 99,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>573420</t>
+          <t>571982</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>617362</t>
+          <t>616032</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>814127</t>
+          <t>813229</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>860013</t>
+          <t>859184</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1397405</t>
+          <t>1401113</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1463507</t>
+          <t>1465147</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,23%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>135018</t>
+          <t>136348</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>178960</t>
+          <t>180398</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>126983</t>
+          <t>127812</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>172869</t>
+          <t>173767</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>275868</t>
+          <t>274228</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>341970</t>
+          <t>338262</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1621007</t>
+          <t>1619949</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1696395</t>
+          <t>1694765</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1610421</t>
+          <t>1610022</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1677291</t>
+          <t>1677588</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3254295</t>
+          <t>3252768</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3350508</t>
+          <t>3350336</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>366437</t>
+          <t>368067</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>441825</t>
+          <t>442883</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>300423</t>
+          <t>300126</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>367293</t>
+          <t>367692</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>690037</t>
+          <t>690209</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>786250</t>
+          <t>787777</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,5%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>380089</t>
+          <t>380338</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>421648</t>
+          <t>423452</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>372787</t>
+          <t>372748</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>415530</t>
+          <t>415365</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>763274</t>
+          <t>763615</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>824867</t>
+          <t>824232</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,65%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>123357</t>
+          <t>121553</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>164916</t>
+          <t>164667</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>128999</t>
+          <t>129164</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>171742</t>
+          <t>171781</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>264667</t>
+          <t>265302</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>326260</t>
+          <t>325919</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,91%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2601080</t>
+          <t>2606043</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2699068</t>
+          <t>2698657</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2828127</t>
+          <t>2836470</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2926737</t>
+          <t>2927444</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5464599</t>
+          <t>5464585</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5598177</t>
+          <t>5598072</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>661148</t>
+          <t>661559</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>759136</t>
+          <t>754173</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>582502</t>
+          <t>581795</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>681112</t>
+          <t>672769</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1271278</t>
+          <t>1271383</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1404856</t>
+          <t>1404870</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo confidencial bajo (Duke) en 2023</t>
+          <t>Población con apoyo confidencial bajo (Duke) en 2023 (tasa de respuesta: 98,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>314193</t>
+          <t>313648</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>353662</t>
+          <t>353929</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>495335</t>
+          <t>495400</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>537173</t>
+          <t>533111</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>819337</t>
+          <t>821031</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>875259</t>
+          <t>876245</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,37%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>152555</t>
+          <t>152288</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>192024</t>
+          <t>192569</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>201829</t>
+          <t>205891</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>243667</t>
+          <t>243602</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>369959</t>
+          <t>368973</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>425881</t>
+          <t>424187</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>841389</t>
+          <t>808843</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1398233</t>
+          <t>1406198</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1050883</t>
+          <t>1075552</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1270987</t>
+          <t>1273263</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1981449</t>
+          <t>1970026</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2626824</t>
+          <t>2606910</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>60,83%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>879134</t>
+          <t>871169</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1435978</t>
+          <t>1468524</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>737238</t>
+          <t>734962</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>957342</t>
+          <t>932673</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1658768</t>
+          <t>1678682</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2304143</t>
+          <t>2315566</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>54,03%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>345056</t>
+          <t>345936</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>399519</t>
+          <t>400580</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>337137</t>
+          <t>337318</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>379805</t>
+          <t>384051</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>694609</t>
+          <t>695041</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>762658</t>
+          <t>766347</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>59,2%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>238198</t>
+          <t>237137</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>292661</t>
+          <t>291781</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>277022</t>
+          <t>272776</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>319690</t>
+          <t>319509</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>531885</t>
+          <t>528196</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>599934</t>
+          <t>599502</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,31%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1462267</t>
+          <t>1516409</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2116849</t>
+          <t>2111078</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1943043</t>
+          <t>1930411</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2153522</t>
+          <t>2156794</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3466419</t>
+          <t>3567732</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4222045</t>
+          <t>4219693</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>61,82%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1304451</t>
+          <t>1310222</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1959033</t>
+          <t>1904891</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1250531</t>
+          <t>1247259</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1461010</t>
+          <t>1473642</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2603308</t>
+          <t>2605660</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3358934</t>
+          <t>3257621</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>47,73%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57_AC_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P57_AC_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>736167</t>
+          <t>734086</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>792507</t>
+          <t>790728</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>993030</t>
+          <t>996198</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1051308</t>
+          <t>1054052</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1750425</t>
+          <t>1750064</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1829589</t>
+          <t>1830585</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>78,0%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>239216</t>
+          <t>240995</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>295556</t>
+          <t>297637</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>263805</t>
+          <t>261061</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>322083</t>
+          <t>318915</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>517246</t>
+          <t>516250</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>596410</t>
+          <t>596771</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1050497</t>
+          <t>1053219</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1130738</t>
+          <t>1133779</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1028919</t>
+          <t>1027830</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1101192</t>
+          <t>1100844</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2105424</t>
+          <t>2109476</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2213999</t>
+          <t>2216860</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,61%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>562675</t>
+          <t>559634</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>642916</t>
+          <t>640194</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>484350</t>
+          <t>484698</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>556623</t>
+          <t>557712</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1064956</t>
+          <t>1062095</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1173531</t>
+          <t>1169479</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,67%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>343119</t>
+          <t>345112</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>389365</t>
+          <t>389794</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>274122</t>
+          <t>276479</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>316966</t>
+          <t>318751</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>632411</t>
+          <t>635490</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>695823</t>
+          <t>695843</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>159408</t>
+          <t>158979</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>205654</t>
+          <t>203661</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>159446</t>
+          <t>157661</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>202290</t>
+          <t>199933</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>329362</t>
+          <t>329342</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>392774</t>
+          <t>389695</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,01%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2172811</t>
+          <t>2179290</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2281084</t>
+          <t>2280419</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2334164</t>
+          <t>2336294</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2444053</t>
+          <t>2438619</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4540249</t>
+          <t>4532346</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4681898</t>
+          <t>4684354</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,43%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>992825</t>
+          <t>993490</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1101098</t>
+          <t>1094619</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>933013</t>
+          <t>938447</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1042902</t>
+          <t>1040772</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1969077</t>
+          <t>1966621</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2110726</t>
+          <t>2118629</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,85%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>646955</t>
+          <t>648516</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>705347</t>
+          <t>705384</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>974431</t>
+          <t>975333</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1039179</t>
+          <t>1040139</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1644301</t>
+          <t>1643203</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1734744</t>
+          <t>1729902</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,53%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>256410</t>
+          <t>256373</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>314802</t>
+          <t>313241</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>289390</t>
+          <t>288430</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>354138</t>
+          <t>353236</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>555582</t>
+          <t>560424</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>646025</t>
+          <t>647123</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,25%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1225536</t>
+          <t>1221529</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1312062</t>
+          <t>1308420</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1245026</t>
+          <t>1245641</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1325305</t>
+          <t>1322852</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2489227</t>
+          <t>2490244</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2608103</t>
+          <t>2611411</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,5%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>640773</t>
+          <t>644415</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>727299</t>
+          <t>731306</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>425757</t>
+          <t>428210</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>506036</t>
+          <t>505421</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1095794</t>
+          <t>1092486</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1214670</t>
+          <t>1213653</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,77%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>278510</t>
+          <t>281227</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>323951</t>
+          <t>327656</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>268891</t>
+          <t>270373</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>311597</t>
+          <t>318456</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>562693</t>
+          <t>562743</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>627297</t>
+          <t>626473</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,22%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>153458</t>
+          <t>149753</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>198899</t>
+          <t>196182</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>142925</t>
+          <t>136066</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>185631</t>
+          <t>184149</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>304634</t>
+          <t>305458</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>369238</t>
+          <t>369188</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2194927</t>
+          <t>2190961</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2303614</t>
+          <t>2310541</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2531121</t>
+          <t>2531503</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2635431</t>
+          <t>2638353</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4756135</t>
+          <t>4755446</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4916123</t>
+          <t>4916049</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1088386</t>
+          <t>1081459</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1197073</t>
+          <t>1201039</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>898722</t>
+          <t>895800</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1003032</t>
+          <t>1002650</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2010031</t>
+          <t>2010105</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2170019</t>
+          <t>2170708</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,34%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>571982</t>
+          <t>573473</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>616032</t>
+          <t>617453</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>813229</t>
+          <t>812763</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>859184</t>
+          <t>859030</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1401113</t>
+          <t>1400858</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1465147</t>
+          <t>1462901</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,1%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>136348</t>
+          <t>134927</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>180398</t>
+          <t>178907</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>127812</t>
+          <t>127966</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>173767</t>
+          <t>174233</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>274228</t>
+          <t>276474</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>338262</t>
+          <t>338517</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1619949</t>
+          <t>1619785</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1694765</t>
+          <t>1693188</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1610022</t>
+          <t>1613586</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1677588</t>
+          <t>1677039</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3252768</t>
+          <t>3256417</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3350336</t>
+          <t>3350146</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,91%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>368067</t>
+          <t>369644</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>442883</t>
+          <t>443047</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>300126</t>
+          <t>300675</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>367692</t>
+          <t>364128</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>690209</t>
+          <t>690399</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>787777</t>
+          <t>784128</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>380338</t>
+          <t>380400</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>423452</t>
+          <t>423630</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>372748</t>
+          <t>374729</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>415365</t>
+          <t>417208</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>763615</t>
+          <t>767751</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>824232</t>
+          <t>825025</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,72%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>121553</t>
+          <t>121375</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>164667</t>
+          <t>164605</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>129164</t>
+          <t>127321</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>171781</t>
+          <t>169800</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>265302</t>
+          <t>264509</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>325919</t>
+          <t>321783</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,53%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2606043</t>
+          <t>2608273</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2698657</t>
+          <t>2699653</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2836470</t>
+          <t>2836967</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2927444</t>
+          <t>2923631</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5464585</t>
+          <t>5467893</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5598072</t>
+          <t>5597998</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>661559</t>
+          <t>660563</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>754173</t>
+          <t>751943</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>581795</t>
+          <t>585608</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>672769</t>
+          <t>672272</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1271383</t>
+          <t>1271457</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1404870</t>
+          <t>1401562</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
@@ -5537,27 +5537,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>334615</t>
+          <t>376421</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>313648</t>
+          <t>352715</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>353929</t>
+          <t>397948</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>515233</t>
+          <t>569337</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>495400</t>
+          <t>549434</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>533111</t>
+          <t>591096</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>849847</t>
+          <t>945759</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>821031</t>
+          <t>912856</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>876245</t>
+          <t>973201</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,9%</t>
         </is>
       </c>
     </row>
@@ -5650,22 +5650,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>171602</t>
+          <t>192751</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>152288</t>
+          <t>171224</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>192569</t>
+          <t>216457</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>223769</t>
+          <t>234142</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>205891</t>
+          <t>212383</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>243602</t>
+          <t>254045</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>395371</t>
+          <t>426893</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>368973</t>
+          <t>399451</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>424187</t>
+          <t>459796</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,5%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>506217</t>
+          <t>569172</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>506217</t>
+          <t>569172</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>506217</t>
+          <t>569172</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>739002</t>
+          <t>803479</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>739002</t>
+          <t>803479</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>739002</t>
+          <t>803479</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1245218</t>
+          <t>1372652</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1245218</t>
+          <t>1372652</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1245218</t>
+          <t>1372652</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1237277</t>
+          <t>1383791</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>808843</t>
+          <t>1330359</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1406198</t>
+          <t>1437415</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1205705</t>
+          <t>1374046</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1075552</t>
+          <t>1334730</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1273263</t>
+          <t>1415451</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2442983</t>
+          <t>2757837</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1970026</t>
+          <t>2685689</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2606910</t>
+          <t>2820584</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>64,69%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1040090</t>
+          <t>831857</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>871169</t>
+          <t>778233</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1468524</t>
+          <t>885289</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>802520</t>
+          <t>770415</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>734962</t>
+          <t>729010</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>932673</t>
+          <t>809731</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1842609</t>
+          <t>1602272</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1678682</t>
+          <t>1539525</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2315566</t>
+          <t>1674420</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>38,4%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2277367</t>
+          <t>2215648</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2277367</t>
+          <t>2215648</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2277367</t>
+          <t>2215648</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2008225</t>
+          <t>2144461</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2008225</t>
+          <t>2144461</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2008225</t>
+          <t>2144461</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4285592</t>
+          <t>4360109</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4285592</t>
+          <t>4360109</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4285592</t>
+          <t>4360109</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>371612</t>
+          <t>415344</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>345936</t>
+          <t>386895</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>400580</t>
+          <t>444693</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>358446</t>
+          <t>406122</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>337318</t>
+          <t>381053</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>384051</t>
+          <t>431640</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>730057</t>
+          <t>821467</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>695041</t>
+          <t>784882</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>766347</t>
+          <t>858907</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>60,02%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>266105</t>
+          <t>285901</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>237137</t>
+          <t>256552</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>291781</t>
+          <t>314350</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>298381</t>
+          <t>323640</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>272776</t>
+          <t>298122</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>319509</t>
+          <t>348709</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>564486</t>
+          <t>609540</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>528196</t>
+          <t>572100</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>599502</t>
+          <t>646125</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>45,15%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>637717</t>
+          <t>701245</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>637717</t>
+          <t>701245</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>637717</t>
+          <t>701245</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>656827</t>
+          <t>729762</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>656827</t>
+          <t>729762</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>656827</t>
+          <t>729762</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1294543</t>
+          <t>1431007</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1294543</t>
+          <t>1431007</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1294543</t>
+          <t>1431007</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1943503</t>
+          <t>2175557</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1516409</t>
+          <t>2106635</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2111078</t>
+          <t>2239873</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2079384</t>
+          <t>2349505</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1930411</t>
+          <t>2294906</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2156794</t>
+          <t>2401690</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4022886</t>
+          <t>4525062</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3567732</t>
+          <t>4435056</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4219693</t>
+          <t>4613375</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>64,4%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1477797</t>
+          <t>1310508</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1310222</t>
+          <t>1246192</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1904891</t>
+          <t>1379430</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1324669</t>
+          <t>1328197</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1247259</t>
+          <t>1276012</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1473642</t>
+          <t>1382796</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2802467</t>
+          <t>2638705</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2605660</t>
+          <t>2550392</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3257621</t>
+          <t>2728711</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>38,09%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3421300</t>
+          <t>3486065</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3421300</t>
+          <t>3486065</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3421300</t>
+          <t>3486065</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3404053</t>
+          <t>3677702</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3404053</t>
+          <t>3677702</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3404053</t>
+          <t>3677702</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6825353</t>
+          <t>7163767</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6825353</t>
+          <t>7163767</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6825353</t>
+          <t>7163767</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
